--- a/gte/nodes/P/compressor_blade_self_frequency.xlsx
+++ b/gte/nodes/P/compressor_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>53.645413302299588</v>
+        <v>54.21548417113474</v>
       </c>
       <c r="C3">
-        <v>336.21433166860152</v>
+        <v>339.78716267819937</v>
       </c>
       <c r="D3">
-        <v>941.50456527659242</v>
+        <v>951.50960191439344</v>
       </c>
       <c r="E3">
-        <v>1846.3559138355913</v>
+        <v>1865.9764863167443</v>
       </c>
       <c r="F3">
-        <v>3050.9063047101045</v>
+        <v>3083.3272089551683</v>
       </c>
       <c r="G3">
-        <v>4556.3547248086406</v>
+        <v>4604.773497948775</v>
       </c>
       <c r="H3">
-        <v>314.383983744998</v>
+        <v>261.96031873032894</v>
       </c>
       <c r="I3">
-        <v>943.15195123499393</v>
+        <v>785.88095619098669</v>
       </c>
       <c r="J3">
-        <v>1571.9199187249899</v>
+        <v>1309.8015936516447</v>
       </c>
       <c r="K3">
-        <v>2200.6878862149861</v>
+        <v>1833.7222311123026</v>
       </c>
       <c r="L3">
-        <v>2829.4558537049816</v>
+        <v>2357.64286857296</v>
       </c>
       <c r="M3">
-        <v>3458.223821194978</v>
+        <v>2881.5635060336181</v>
       </c>
       <c r="N3">
-        <v>628.767967489996</v>
+        <v>523.92063746065787</v>
       </c>
       <c r="O3">
-        <v>1257.5359349799919</v>
+        <v>1047.8412749213157</v>
       </c>
       <c r="P3">
-        <v>1886.3039024699879</v>
+        <v>1571.7619123819734</v>
       </c>
       <c r="Q3">
-        <v>2515.0718699599838</v>
+        <v>2095.6825498426315</v>
       </c>
       <c r="R3">
-        <v>3143.8398374499798</v>
+        <v>2619.6031873032894</v>
       </c>
       <c r="S3">
-        <v>3772.6078049399757</v>
+        <v>3143.5238247639468</v>
       </c>
     </row>
   </sheetData>
